--- a/DG/data/Arg.xlsx
+++ b/DG/data/Arg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2489b4ab3e3a2fa6/Escritorio/David Guzzi/Github/MECTMT11/DG/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{9016ADDD-22A1-4240-AACE-AEB2F52293FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22A06444-E0A5-4D40-899D-5B053D9D2652}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{9016ADDD-22A1-4240-AACE-AEB2F52293FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291215CE-34D8-4CA0-9EDF-D04BBE6BDFAF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A9E7A37D-4260-4CB4-8811-068D8D482F08}"/>
   </bookViews>
@@ -46,6 +46,102 @@
     <author>David Guzzi</author>
   </authors>
   <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{613D32B2-F5EF-46E1-A0B3-A4D6A69657FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>David Guzzi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Se parte de la población total anual y se la convierte en una serie trimestral mediante interpolación lineal entre años consecutivos.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{C945D71E-8782-4C4B-9A02-D5A1498D2125}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>David Guzzi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Desde 200401 a 201809 es LEBAC; desde 201810 a 202312 es LELIQ; desde 202401 a 202406 es Pases Pasivos; de allí es LEFI. Todas las tasas fueron expresadas en TNA a 30 días; luego promedioss aritméticos. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{539EE1A6-5444-4CEF-9186-5B351F7836F2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>David Guzzi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Se empalmaron las distintas series del índice salarial (cambios de base y anexos metodológicos) utilizando un coeficiente de enlace en el período de superposición, para construir una única serie homogénea.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{224D1671-DAD4-4B3C-B764-58ED47583FDF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>David Guzzi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Se construyeron las horas a partir de la EPH filtrando por condición ACTIVO = ocupado, usando PONDERA como factor de expansión y calculando promedios ponderados tanto de PP3E_TOT (horas habituales) como de PP3F_TOT (horas efectivas).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="O3" authorId="0" shapeId="0" xr:uid="{74BB9A01-329F-408F-939D-3F528E518299}">
       <text>
         <r>
@@ -77,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="158">
   <si>
     <t>Original data</t>
   </si>
@@ -508,16 +604,7 @@
     <t>población</t>
   </si>
   <si>
-    <t>pbi real ($ millones) base 2004</t>
-  </si>
-  <si>
     <t>pbi nominal ($ millones) base 2004</t>
-  </si>
-  <si>
-    <t>consumo privado real ($ millones) base 2004</t>
-  </si>
-  <si>
-    <t>inversión real ($ millones) base 2004</t>
   </si>
   <si>
     <t>índice de salarios nominal prom trimestral base 2004</t>
@@ -546,6 +633,42 @@
   <si>
     <t>Horas sin 2020</t>
   </si>
+  <si>
+    <t>fuente</t>
+  </si>
+  <si>
+    <t>https://www.indec.gob.ar/ftp/cuadros/economia/sh_oferta_demanda_desest_12_25.xls</t>
+  </si>
+  <si>
+    <t>pbi real ($ millones) base 2004 deses</t>
+  </si>
+  <si>
+    <t>consumo privado real ($ millones) base 2004 deses</t>
+  </si>
+  <si>
+    <t>inversión real ($ millones) base 2004 deses</t>
+  </si>
+  <si>
+    <t>https://www.indec.gob.ar/ftp/cuadros/economia/sh_oferta_demanda_12_25.xls</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>https://datos.bancomundial.org/indicador/SP.POP.TOTL?locations=AR</t>
+  </si>
+  <si>
+    <t>https://www.bcra.gob.ar/operaciones-pases-subastas-letras/</t>
+  </si>
+  <si>
+    <t>https://www.indec.gob.ar/indec/web/Nivel4-Tema-4-31-61</t>
+  </si>
+  <si>
+    <t>https://www.argentina.gob.ar/trabajo/estadisticas/mercado-de-trabajo-0</t>
+  </si>
+  <si>
+    <t>https://www.indec.gob.ar/indec/web/Institucional-Indec-BasesDeDatos</t>
+  </si>
 </sst>
 </file>
 
@@ -555,7 +678,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -614,6 +737,25 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -638,14 +780,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -670,8 +813,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{FD3471AA-5A90-4348-8330-26C4A7CEB9BF}"/>
@@ -24814,18 +24965,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="W8:AC237">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.17" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
@@ -24848,8 +24987,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="J1">
-        <v>100</v>
+      <c r="B1" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="P1" t="s">
+        <v>152</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -24858,16 +25035,16 @@
         <v>46</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>134</v>
@@ -24876,28 +25053,28 @@
         <v>135</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="M2" t="s">
-        <v>142</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>13</v>
@@ -25086,7 +25263,7 @@
         <v>1305.7946563524383</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="0"/>
+        <f>LN((P4*N4/100)/I4)*100</f>
         <v>3.254094680533496</v>
       </c>
       <c r="W4" s="6">
@@ -25094,26 +25271,26 @@
         <v>16.130007779576871</v>
       </c>
       <c r="X4" s="6">
-        <f t="shared" ref="X4:X67" si="8">LN(L4)*100</f>
+        <f>LN(L4)*100</f>
         <v>452.18857446283118</v>
       </c>
       <c r="Y4" s="6">
-        <f t="shared" ref="Y4:Y67" si="9">J4/4</f>
+        <f t="shared" ref="Y4:Y67" si="8">J4/4</f>
         <v>1.3455462829930371</v>
       </c>
       <c r="AB4">
         <v>1</v>
       </c>
       <c r="AC4" s="6">
-        <f t="shared" ref="AC4:AC35" si="10">S4-S3</f>
+        <f t="shared" ref="AC4:AC35" si="9">S4-S3</f>
         <v>0.26511591087728448</v>
       </c>
       <c r="AD4" s="6">
-        <f t="shared" ref="AD4:AD35" si="11">T4-T3</f>
+        <f t="shared" ref="AD4:AD35" si="10">T4-T3</f>
         <v>2.8753848925914554</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" ref="AE4:AE35" si="12">U4-U3</f>
+        <f t="shared" ref="AE4:AE35" si="11">U4-U3</f>
         <v>-1.5386968404202435</v>
       </c>
       <c r="AF4" s="6">
@@ -25201,15 +25378,15 @@
         <v>5.0132650575882964</v>
       </c>
       <c r="W5" s="6">
-        <f t="shared" ref="W5:W68" si="13">(LN(G5)-LN(G4))*100</f>
+        <f t="shared" ref="W5:W68" si="12">(LN(G5)-LN(G4))*100</f>
         <v>-9.1719930464343236</v>
       </c>
       <c r="X5" s="6">
+        <f t="shared" ref="X4:X67" si="13">LN(L5)*100</f>
+        <v>462.22992165221495</v>
+      </c>
+      <c r="Y5" s="6">
         <f t="shared" si="8"/>
-        <v>462.22992165221495</v>
-      </c>
-      <c r="Y5" s="6">
-        <f t="shared" si="9"/>
         <v>1.6582700431170772</v>
       </c>
       <c r="AB5">
@@ -25217,15 +25394,15 @@
         <v>2</v>
       </c>
       <c r="AC5" s="6">
+        <f t="shared" si="9"/>
+        <v>3.7834527049933513</v>
+      </c>
+      <c r="AD5" s="6">
         <f t="shared" si="10"/>
-        <v>3.7834527049933513</v>
-      </c>
-      <c r="AD5" s="6">
+        <v>0.95840760369219424</v>
+      </c>
+      <c r="AE5" s="6">
         <f t="shared" si="11"/>
-        <v>0.95840760369219424</v>
-      </c>
-      <c r="AE5" s="6">
-        <f t="shared" si="12"/>
         <v>4.6986519720107935</v>
       </c>
       <c r="AF5" s="6">
@@ -25313,15 +25490,15 @@
         <v>5.7114331612695786</v>
       </c>
       <c r="W6" s="6">
+        <f t="shared" si="12"/>
+        <v>1.6678087844468337</v>
+      </c>
+      <c r="X6" s="6">
         <f t="shared" si="13"/>
-        <v>1.6678087844468337</v>
-      </c>
-      <c r="X6" s="6">
+        <v>461.74749451420888</v>
+      </c>
+      <c r="Y6" s="6">
         <f t="shared" si="8"/>
-        <v>461.74749451420888</v>
-      </c>
-      <c r="Y6" s="6">
-        <f t="shared" si="9"/>
         <v>1.4211788826474436</v>
       </c>
       <c r="AB6">
@@ -25329,15 +25506,15 @@
         <v>3</v>
       </c>
       <c r="AC6" s="6">
+        <f t="shared" si="9"/>
+        <v>2.0386775848319303</v>
+      </c>
+      <c r="AD6" s="6">
         <f t="shared" si="10"/>
-        <v>2.0386775848319303</v>
-      </c>
-      <c r="AD6" s="6">
+        <v>1.5587248205883952</v>
+      </c>
+      <c r="AE6" s="6">
         <f t="shared" si="11"/>
-        <v>1.5587248205883952</v>
-      </c>
-      <c r="AE6" s="6">
-        <f t="shared" si="12"/>
         <v>1.0684904438314788</v>
       </c>
       <c r="AF6" s="6">
@@ -25425,15 +25602,15 @@
         <v>4.1902670260969321</v>
       </c>
       <c r="W7" s="6">
+        <f t="shared" si="12"/>
+        <v>-1.397078476965774</v>
+      </c>
+      <c r="X7" s="6">
         <f t="shared" si="13"/>
-        <v>-1.397078476965774</v>
-      </c>
-      <c r="X7" s="6">
+        <v>470.30636835495301</v>
+      </c>
+      <c r="Y7" s="6">
         <f t="shared" si="8"/>
-        <v>470.30636835495301</v>
-      </c>
-      <c r="Y7" s="6">
-        <f t="shared" si="9"/>
         <v>1.1706151800544966</v>
       </c>
       <c r="AB7">
@@ -25441,15 +25618,15 @@
         <v>4</v>
       </c>
       <c r="AC7" s="6">
+        <f t="shared" si="9"/>
+        <v>-1.9024039573300797</v>
+      </c>
+      <c r="AD7" s="6">
         <f t="shared" si="10"/>
-        <v>-1.9024039573300797</v>
-      </c>
-      <c r="AD7" s="6">
+        <v>6.9762941420701736</v>
+      </c>
+      <c r="AE7" s="6">
         <f t="shared" si="11"/>
-        <v>6.9762941420701736</v>
-      </c>
-      <c r="AE7" s="6">
-        <f t="shared" si="12"/>
         <v>2.5997085372325728</v>
       </c>
       <c r="AF7" s="6">
@@ -25537,15 +25714,15 @@
         <v>3.2724886234296093</v>
       </c>
       <c r="W8" s="6">
+        <f t="shared" si="12"/>
+        <v>14.752555454037175</v>
+      </c>
+      <c r="X8" s="6">
         <f t="shared" si="13"/>
-        <v>14.752555454037175</v>
-      </c>
-      <c r="X8" s="6">
+        <v>460.02071465863884</v>
+      </c>
+      <c r="Y8" s="6">
         <f t="shared" si="8"/>
-        <v>460.02071465863884</v>
-      </c>
-      <c r="Y8" s="6">
-        <f t="shared" si="9"/>
         <v>1.5352595903228112</v>
       </c>
       <c r="AB8">
@@ -25553,15 +25730,15 @@
         <v>5</v>
       </c>
       <c r="AC8" s="6">
+        <f t="shared" si="9"/>
+        <v>8.0695762902471415</v>
+      </c>
+      <c r="AD8" s="6">
         <f t="shared" si="10"/>
-        <v>8.0695762902471415</v>
-      </c>
-      <c r="AD8" s="6">
+        <v>2.9959598837906469</v>
+      </c>
+      <c r="AE8" s="6">
         <f t="shared" si="11"/>
-        <v>2.9959598837906469</v>
-      </c>
-      <c r="AE8" s="6">
-        <f t="shared" si="12"/>
         <v>2.0618090008972558</v>
       </c>
       <c r="AF8" s="6">
@@ -25649,15 +25826,15 @@
         <v>14.107986593935401</v>
       </c>
       <c r="W9" s="6">
+        <f t="shared" si="12"/>
+        <v>-3.1757495836219896</v>
+      </c>
+      <c r="X9" s="6">
         <f t="shared" si="13"/>
-        <v>-3.1757495836219896</v>
-      </c>
-      <c r="X9" s="6">
+        <v>468.73543972253844</v>
+      </c>
+      <c r="Y9" s="6">
         <f t="shared" si="8"/>
-        <v>468.73543972253844</v>
-      </c>
-      <c r="Y9" s="6">
-        <f t="shared" si="9"/>
         <v>1.8139916240145906</v>
       </c>
       <c r="AB9">
@@ -25665,15 +25842,15 @@
         <v>6</v>
       </c>
       <c r="AC9" s="6">
+        <f t="shared" si="9"/>
+        <v>-4.7853326356619164</v>
+      </c>
+      <c r="AD9" s="6">
         <f t="shared" si="10"/>
-        <v>-4.7853326356619164</v>
-      </c>
-      <c r="AD9" s="6">
+        <v>1.5464834687463735E-2</v>
+      </c>
+      <c r="AE9" s="6">
         <f t="shared" si="11"/>
-        <v>1.5464834687463735E-2</v>
-      </c>
-      <c r="AE9" s="6">
-        <f t="shared" si="12"/>
         <v>0.31781710170503175</v>
       </c>
       <c r="AF9" s="6">
@@ -25761,15 +25938,15 @@
         <v>10.84249132054345</v>
       </c>
       <c r="W10" s="6">
+        <f t="shared" si="12"/>
+        <v>3.6154877833755705</v>
+      </c>
+      <c r="X10" s="6">
         <f t="shared" si="13"/>
-        <v>3.6154877833755705</v>
-      </c>
-      <c r="X10" s="6">
+        <v>470.08291417133597</v>
+      </c>
+      <c r="Y10" s="6">
         <f t="shared" si="8"/>
-        <v>470.08291417133597</v>
-      </c>
-      <c r="Y10" s="6">
-        <f t="shared" si="9"/>
         <v>1.8918454517247687</v>
       </c>
       <c r="AB10">
@@ -25777,15 +25954,15 @@
         <v>7</v>
       </c>
       <c r="AC10" s="6">
+        <f t="shared" si="9"/>
+        <v>3.3873713131249588</v>
+      </c>
+      <c r="AD10" s="6">
         <f t="shared" si="10"/>
-        <v>3.3873713131249588</v>
-      </c>
-      <c r="AD10" s="6">
+        <v>7.9907135538251168</v>
+      </c>
+      <c r="AE10" s="6">
         <f t="shared" si="11"/>
-        <v>7.9907135538251168</v>
-      </c>
-      <c r="AE10" s="6">
-        <f t="shared" si="12"/>
         <v>1.6061189834711058</v>
       </c>
       <c r="AF10" s="6">
@@ -25873,15 +26050,15 @@
         <v>6.7741300953638204</v>
       </c>
       <c r="W11" s="6">
+        <f t="shared" si="12"/>
+        <v>0.53756970963600992</v>
+      </c>
+      <c r="X11" s="6">
         <f t="shared" si="13"/>
-        <v>0.53756970963600992</v>
-      </c>
-      <c r="X11" s="6">
+        <v>473.61925963143233</v>
+      </c>
+      <c r="Y11" s="6">
         <f t="shared" si="8"/>
-        <v>473.61925963143233</v>
-      </c>
-      <c r="Y11" s="6">
-        <f t="shared" si="9"/>
         <v>1.7668622078968466</v>
       </c>
       <c r="AB11">
@@ -25889,15 +26066,15 @@
         <v>8</v>
       </c>
       <c r="AC11" s="6">
+        <f t="shared" si="9"/>
+        <v>2.5771602376919418</v>
+      </c>
+      <c r="AD11" s="6">
         <f t="shared" si="10"/>
-        <v>2.5771602376919418</v>
-      </c>
-      <c r="AD11" s="6">
+        <v>1.429769225940845</v>
+      </c>
+      <c r="AE11" s="6">
         <f t="shared" si="11"/>
-        <v>1.429769225940845</v>
-      </c>
-      <c r="AE11" s="6">
-        <f t="shared" si="12"/>
         <v>2.3791355706596278</v>
       </c>
       <c r="AF11" s="6">
@@ -25985,15 +26162,15 @@
         <v>16.418655159442004</v>
       </c>
       <c r="W12" s="6">
+        <f t="shared" si="12"/>
+        <v>11.130726577962058</v>
+      </c>
+      <c r="X12" s="6">
         <f t="shared" si="13"/>
-        <v>11.130726577962058</v>
-      </c>
-      <c r="X12" s="6">
+        <v>467.240546761784</v>
+      </c>
+      <c r="Y12" s="6">
         <f t="shared" si="8"/>
-        <v>467.240546761784</v>
-      </c>
-      <c r="Y12" s="6">
-        <f t="shared" si="9"/>
         <v>2.0921772339150868</v>
       </c>
       <c r="AB12">
@@ -26001,15 +26178,15 @@
         <v>9</v>
       </c>
       <c r="AC12" s="6">
+        <f t="shared" si="9"/>
+        <v>4.827815624930281</v>
+      </c>
+      <c r="AD12" s="6">
         <f t="shared" si="10"/>
-        <v>4.827815624930281</v>
-      </c>
-      <c r="AD12" s="6">
+        <v>3.0723383924084828</v>
+      </c>
+      <c r="AE12" s="6">
         <f t="shared" si="11"/>
-        <v>3.0723383924084828</v>
-      </c>
-      <c r="AE12" s="6">
-        <f t="shared" si="12"/>
         <v>0.94822145005241509</v>
       </c>
       <c r="AF12" s="6">
@@ -26097,15 +26274,15 @@
         <v>16.19230755589648</v>
       </c>
       <c r="W13" s="6">
+        <f t="shared" si="12"/>
+        <v>-2.6148240004415513</v>
+      </c>
+      <c r="X13" s="6">
         <f t="shared" si="13"/>
-        <v>-2.6148240004415513</v>
-      </c>
-      <c r="X13" s="6">
+        <v>475.23699566318214</v>
+      </c>
+      <c r="Y13" s="6">
         <f t="shared" si="8"/>
-        <v>475.23699566318214</v>
-      </c>
-      <c r="Y13" s="6">
-        <f t="shared" si="9"/>
         <v>2.4716758910024565</v>
       </c>
       <c r="AB13">
@@ -26113,15 +26290,15 @@
         <v>10</v>
       </c>
       <c r="AC13" s="6">
+        <f t="shared" si="9"/>
+        <v>2.2030801690739281</v>
+      </c>
+      <c r="AD13" s="6">
         <f t="shared" si="10"/>
-        <v>2.2030801690739281</v>
-      </c>
-      <c r="AD13" s="6">
+        <v>2.8665033549204963</v>
+      </c>
+      <c r="AE13" s="6">
         <f t="shared" si="11"/>
-        <v>2.8665033549204963</v>
-      </c>
-      <c r="AE13" s="6">
-        <f t="shared" si="12"/>
         <v>2.5468771402877337</v>
       </c>
       <c r="AF13" s="6">
@@ -26209,15 +26386,15 @@
         <v>13.082135743958318</v>
       </c>
       <c r="W14" s="6">
+        <f t="shared" si="12"/>
+        <v>2.3645134936361778</v>
+      </c>
+      <c r="X14" s="6">
         <f t="shared" si="13"/>
-        <v>2.3645134936361778</v>
-      </c>
-      <c r="X14" s="6">
+        <v>476.58953456599738</v>
+      </c>
+      <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>476.58953456599738</v>
-      </c>
-      <c r="Y14" s="6">
-        <f t="shared" si="9"/>
         <v>2.4595304757229175</v>
       </c>
       <c r="AB14">
@@ -26225,15 +26402,15 @@
         <v>11</v>
       </c>
       <c r="AC14" s="6">
+        <f t="shared" si="9"/>
+        <v>-0.3001073508976333</v>
+      </c>
+      <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>-0.3001073508976333</v>
-      </c>
-      <c r="AD14" s="6">
+        <v>2.4890000827151653</v>
+      </c>
+      <c r="AE14" s="6">
         <f t="shared" si="11"/>
-        <v>2.4890000827151653</v>
-      </c>
-      <c r="AE14" s="6">
-        <f t="shared" si="12"/>
         <v>1.8743957605531705</v>
       </c>
       <c r="AF14" s="6">
@@ -26321,15 +26498,15 @@
         <v>10.11495600159693</v>
       </c>
       <c r="W15" s="6">
+        <f t="shared" si="12"/>
+        <v>-0.84912858560564075</v>
+      </c>
+      <c r="X15" s="6">
         <f t="shared" si="13"/>
-        <v>-0.84912858560564075</v>
-      </c>
-      <c r="X15" s="6">
+        <v>480.45213474860907</v>
+      </c>
+      <c r="Y15" s="6">
         <f t="shared" si="8"/>
-        <v>480.45213474860907</v>
-      </c>
-      <c r="Y15" s="6">
-        <f t="shared" si="9"/>
         <v>2.3914750304770447</v>
       </c>
       <c r="AB15">
@@ -26337,15 +26514,15 @@
         <v>12</v>
       </c>
       <c r="AC15" s="6">
+        <f t="shared" si="9"/>
+        <v>2.7819304341614952</v>
+      </c>
+      <c r="AD15" s="6">
         <f t="shared" si="10"/>
-        <v>2.7819304341614952</v>
-      </c>
-      <c r="AD15" s="6">
+        <v>8.2355800052584982</v>
+      </c>
+      <c r="AE15" s="6">
         <f t="shared" si="11"/>
-        <v>8.2355800052584982</v>
-      </c>
-      <c r="AE15" s="6">
-        <f t="shared" si="12"/>
         <v>2.1134967976620374</v>
       </c>
       <c r="AF15" s="6">
@@ -26433,15 +26610,15 @@
         <v>18.629630560738377</v>
       </c>
       <c r="W16" s="6">
+        <f t="shared" si="12"/>
+        <v>13.458100286142471</v>
+      </c>
+      <c r="X16" s="6">
         <f t="shared" si="13"/>
-        <v>13.458100286142471</v>
-      </c>
-      <c r="X16" s="6">
+        <v>471.50428919679513</v>
+      </c>
+      <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>471.50428919679513</v>
-      </c>
-      <c r="Y16" s="6">
-        <f t="shared" si="9"/>
         <v>2.3545423535997259</v>
       </c>
       <c r="AB16">
@@ -26449,15 +26626,15 @@
         <v>13</v>
       </c>
       <c r="AC16" s="6">
+        <f t="shared" si="9"/>
+        <v>2.1746835129815736</v>
+      </c>
+      <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>2.1746835129815736</v>
-      </c>
-      <c r="AD16" s="6">
+        <v>4.1558579434702096</v>
+      </c>
+      <c r="AE16" s="6">
         <f t="shared" si="11"/>
-        <v>4.1558579434702096</v>
-      </c>
-      <c r="AE16" s="6">
-        <f t="shared" si="12"/>
         <v>1.8030891915466327</v>
       </c>
       <c r="AF16" s="6">
@@ -26546,15 +26723,15 @@
         <v>14.950809599675694</v>
       </c>
       <c r="W17" s="6">
+        <f t="shared" si="12"/>
+        <v>-0.27285476994922675</v>
+      </c>
+      <c r="X17" s="6">
         <f t="shared" si="13"/>
-        <v>-0.27285476994922675</v>
-      </c>
-      <c r="X17" s="6">
+        <v>477.56662832097192</v>
+      </c>
+      <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>477.56662832097192</v>
-      </c>
-      <c r="Y17" s="6">
-        <f t="shared" si="9"/>
         <v>2.5475730233521818</v>
       </c>
       <c r="AB17">
@@ -26562,15 +26739,15 @@
         <v>14</v>
       </c>
       <c r="AC17" s="6">
+        <f t="shared" si="9"/>
+        <v>2.1983219879748503</v>
+      </c>
+      <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>2.1983219879748503</v>
-      </c>
-      <c r="AD17" s="6">
+        <v>3.100927063308518</v>
+      </c>
+      <c r="AE17" s="6">
         <f t="shared" si="11"/>
-        <v>3.100927063308518</v>
-      </c>
-      <c r="AE17" s="6">
-        <f t="shared" si="12"/>
         <v>1.0923757871580619</v>
       </c>
       <c r="AF17" s="6">
@@ -26658,15 +26835,15 @@
         <v>9.9377574404743463</v>
       </c>
       <c r="W18" s="6">
+        <f t="shared" si="12"/>
+        <v>5.4413835076505102</v>
+      </c>
+      <c r="X18" s="6">
         <f t="shared" si="13"/>
-        <v>5.4413835076505102</v>
-      </c>
-      <c r="X18" s="6">
+        <v>476.9650634771005</v>
+      </c>
+      <c r="Y18" s="6">
         <f t="shared" si="8"/>
-        <v>476.9650634771005</v>
-      </c>
-      <c r="Y18" s="6">
-        <f t="shared" si="9"/>
         <v>2.6542222059979794</v>
       </c>
       <c r="AB18">
@@ -26674,15 +26851,15 @@
         <v>15</v>
       </c>
       <c r="AC18" s="6">
+        <f t="shared" si="9"/>
+        <v>1.3971929522092523</v>
+      </c>
+      <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>1.3971929522092523</v>
-      </c>
-      <c r="AD18" s="6">
+        <v>2.4837338093677772</v>
+      </c>
+      <c r="AE18" s="6">
         <f t="shared" si="11"/>
-        <v>2.4837338093677772</v>
-      </c>
-      <c r="AE18" s="6">
-        <f t="shared" si="12"/>
         <v>2.7931309815919576</v>
       </c>
       <c r="AF18" s="6">
@@ -26770,15 +26947,15 @@
         <v>14.049740929668564</v>
       </c>
       <c r="W19" s="6">
+        <f t="shared" si="12"/>
+        <v>2.685363721620071</v>
+      </c>
+      <c r="X19" s="6">
         <f t="shared" si="13"/>
-        <v>2.685363721620071</v>
-      </c>
-      <c r="X19" s="6">
+        <v>473.48748278930907</v>
+      </c>
+      <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>473.48748278930907</v>
-      </c>
-      <c r="Y19" s="6">
-        <f t="shared" si="9"/>
         <v>2.674038901073339</v>
       </c>
       <c r="AB19">
@@ -26786,15 +26963,15 @@
         <v>16</v>
       </c>
       <c r="AC19" s="6">
+        <f t="shared" si="9"/>
+        <v>3.7528457720884489</v>
+      </c>
+      <c r="AD19" s="6">
         <f t="shared" si="10"/>
-        <v>3.7528457720884489</v>
-      </c>
-      <c r="AD19" s="6">
+        <v>7.1414769866371444</v>
+      </c>
+      <c r="AE19" s="6">
         <f t="shared" si="11"/>
-        <v>7.1414769866371444</v>
-      </c>
-      <c r="AE19" s="6">
-        <f t="shared" si="12"/>
         <v>0.7392152775453269</v>
       </c>
       <c r="AF19" s="6">
@@ -26882,15 +27059,15 @@
         <v>16.502267579589727</v>
       </c>
       <c r="W20" s="6">
+        <f t="shared" si="12"/>
+        <v>15.705017071372662</v>
+      </c>
+      <c r="X20" s="6">
         <f t="shared" si="13"/>
-        <v>15.705017071372662</v>
-      </c>
-      <c r="X20" s="6">
+        <v>464.55555256634983</v>
+      </c>
+      <c r="Y20" s="6">
         <f t="shared" si="8"/>
-        <v>464.55555256634983</v>
-      </c>
-      <c r="Y20" s="6">
-        <f t="shared" si="9"/>
         <v>2.7244989668283632</v>
       </c>
       <c r="AB20">
@@ -26898,15 +27075,15 @@
         <v>17</v>
       </c>
       <c r="AC20" s="6">
+        <f t="shared" si="9"/>
+        <v>1.3546539510896309</v>
+      </c>
+      <c r="AD20" s="6">
         <f t="shared" si="10"/>
-        <v>1.3546539510896309</v>
-      </c>
-      <c r="AD20" s="6">
+        <v>2.0190930278672568</v>
+      </c>
+      <c r="AE20" s="6">
         <f t="shared" si="11"/>
-        <v>2.0190930278672568</v>
-      </c>
-      <c r="AE20" s="6">
-        <f t="shared" si="12"/>
         <v>0.2280628763205641</v>
       </c>
       <c r="AF20" s="6">
@@ -26994,15 +27171,15 @@
         <v>16.188918737297538</v>
       </c>
       <c r="W21" s="6">
+        <f t="shared" si="12"/>
+        <v>-3.1742263355310385</v>
+      </c>
+      <c r="X21" s="6">
         <f t="shared" si="13"/>
-        <v>-3.1742263355310385</v>
-      </c>
-      <c r="X21" s="6">
+        <v>474.79665124703178</v>
+      </c>
+      <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>474.79665124703178</v>
-      </c>
-      <c r="Y21" s="6">
-        <f t="shared" si="9"/>
         <v>2.8204167802836801</v>
       </c>
       <c r="AB21">
@@ -27010,15 +27187,15 @@
         <v>18</v>
       </c>
       <c r="AC21" s="6">
+        <f t="shared" si="9"/>
+        <v>-2.0731317770155329</v>
+      </c>
+      <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>-2.0731317770155329</v>
-      </c>
-      <c r="AD21" s="6">
+        <v>-6.0786906941173129</v>
+      </c>
+      <c r="AE21" s="6">
         <f t="shared" si="11"/>
-        <v>-6.0786906941173129</v>
-      </c>
-      <c r="AE21" s="6">
-        <f t="shared" si="12"/>
         <v>0.39067709756704971</v>
       </c>
       <c r="AF21" s="6">
@@ -27106,15 +27283,15 @@
         <v>14.402243149221619</v>
       </c>
       <c r="W22" s="6">
+        <f t="shared" si="12"/>
+        <v>3.4152381174689772</v>
+      </c>
+      <c r="X22" s="6">
         <f t="shared" si="13"/>
-        <v>3.4152381174689772</v>
-      </c>
-      <c r="X22" s="6">
+        <v>475.79827872540318</v>
+      </c>
+      <c r="Y22" s="6">
         <f t="shared" si="8"/>
-        <v>475.79827872540318</v>
-      </c>
-      <c r="Y22" s="6">
-        <f t="shared" si="9"/>
         <v>3.0717586185381829</v>
       </c>
       <c r="AB22">
@@ -27122,15 +27299,15 @@
         <v>19</v>
       </c>
       <c r="AC22" s="6">
+        <f t="shared" si="9"/>
+        <v>-1.7417912636628898</v>
+      </c>
+      <c r="AD22" s="6">
         <f t="shared" si="10"/>
-        <v>-1.7417912636628898</v>
-      </c>
-      <c r="AD22" s="6">
+        <v>-11.590107692573383</v>
+      </c>
+      <c r="AE22" s="6">
         <f t="shared" si="11"/>
-        <v>-11.590107692573383</v>
-      </c>
-      <c r="AE22" s="6">
-        <f t="shared" si="12"/>
         <v>-4.9589629409770168</v>
       </c>
       <c r="AF22" s="6">
@@ -27218,15 +27395,15 @@
         <v>24.599126973053401</v>
       </c>
       <c r="W23" s="6">
+        <f t="shared" si="12"/>
+        <v>-1.2856537292615045</v>
+      </c>
+      <c r="X23" s="6">
         <f t="shared" si="13"/>
-        <v>-1.2856537292615045</v>
-      </c>
-      <c r="X23" s="6">
+        <v>479.27857395102018</v>
+      </c>
+      <c r="Y23" s="6">
         <f t="shared" si="8"/>
-        <v>479.27857395102018</v>
-      </c>
-      <c r="Y23" s="6">
-        <f t="shared" si="9"/>
         <v>3.3249444687705987</v>
       </c>
       <c r="AB23">
@@ -27234,15 +27411,15 @@
         <v>20</v>
       </c>
       <c r="AC23" s="6">
+        <f t="shared" si="9"/>
+        <v>-4.7824700545927499</v>
+      </c>
+      <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>-4.7824700545927499</v>
-      </c>
-      <c r="AD23" s="6">
+        <v>-14.731113525819183</v>
+      </c>
+      <c r="AE23" s="6">
         <f t="shared" si="11"/>
-        <v>-14.731113525819183</v>
-      </c>
-      <c r="AE23" s="6">
-        <f t="shared" si="12"/>
         <v>-3.9207007463169248</v>
       </c>
       <c r="AF23" s="6">
@@ -27330,15 +27507,15 @@
         <v>13.135344210859982</v>
       </c>
       <c r="W24" s="6">
+        <f t="shared" si="12"/>
+        <v>14.207550427453075</v>
+      </c>
+      <c r="X24" s="6">
         <f t="shared" si="13"/>
-        <v>14.207550427453075</v>
-      </c>
-      <c r="X24" s="6">
+        <v>468.49334769317181</v>
+      </c>
+      <c r="Y24" s="6">
         <f t="shared" si="8"/>
-        <v>468.49334769317181</v>
-      </c>
-      <c r="Y24" s="6">
-        <f t="shared" si="9"/>
         <v>3.6114583543375351</v>
       </c>
       <c r="AB24">
@@ -27346,15 +27523,15 @@
         <v>21</v>
       </c>
       <c r="AC24" s="6">
+        <f t="shared" si="9"/>
+        <v>-4.5563342248101435</v>
+      </c>
+      <c r="AD24" s="6">
         <f t="shared" si="10"/>
-        <v>-4.5563342248101435</v>
-      </c>
-      <c r="AD24" s="6">
+        <v>-6.0013344099183996</v>
+      </c>
+      <c r="AE24" s="6">
         <f t="shared" si="11"/>
-        <v>-6.0013344099183996</v>
-      </c>
-      <c r="AE24" s="6">
-        <f t="shared" si="12"/>
         <v>-2.6838440801525394</v>
       </c>
       <c r="AF24" s="6">
@@ -27442,15 +27619,15 @@
         <v>15.529691078838786</v>
       </c>
       <c r="W25" s="6">
+        <f t="shared" si="12"/>
+        <v>-2.4145315726205929</v>
+      </c>
+      <c r="X25" s="6">
         <f t="shared" si="13"/>
-        <v>-2.4145315726205929</v>
-      </c>
-      <c r="X25" s="6">
+        <v>476.54129148353877</v>
+      </c>
+      <c r="Y25" s="6">
         <f t="shared" si="8"/>
-        <v>476.54129148353877</v>
-      </c>
-      <c r="Y25" s="6">
-        <f t="shared" si="9"/>
         <v>3.6001371584169308</v>
       </c>
       <c r="AB25">
@@ -27458,15 +27635,15 @@
         <v>22</v>
       </c>
       <c r="AC25" s="6">
+        <f t="shared" si="9"/>
+        <v>7.9671354062343198</v>
+      </c>
+      <c r="AD25" s="6">
         <f t="shared" si="10"/>
-        <v>7.9671354062343198</v>
-      </c>
-      <c r="AD25" s="6">
+        <v>5.1545938883930376</v>
+      </c>
+      <c r="AE25" s="6">
         <f t="shared" si="11"/>
-        <v>5.1545938883930376</v>
-      </c>
-      <c r="AE25" s="6">
-        <f t="shared" si="12"/>
         <v>3.5997776423459982</v>
       </c>
       <c r="AF25" s="6">
@@ -27554,15 +27731,15 @@
         <v>13.5308011444298</v>
       </c>
       <c r="W26" s="6">
+        <f t="shared" si="12"/>
+        <v>4.7328810893786155</v>
+      </c>
+      <c r="X26" s="6">
         <f t="shared" si="13"/>
-        <v>4.7328810893786155</v>
-      </c>
-      <c r="X26" s="6">
+        <v>476.1947298723735</v>
+      </c>
+      <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>476.1947298723735</v>
-      </c>
-      <c r="Y26" s="6">
-        <f t="shared" si="9"/>
         <v>3.4225425070077384</v>
       </c>
       <c r="AB26">
@@ -27570,15 +27747,15 @@
         <v>23</v>
       </c>
       <c r="AC26" s="6">
+        <f t="shared" si="9"/>
+        <v>-1.7142924033244071</v>
+      </c>
+      <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>-1.7142924033244071</v>
-      </c>
-      <c r="AD26" s="6">
+        <v>5.4994855307049875</v>
+      </c>
+      <c r="AE26" s="6">
         <f t="shared" si="11"/>
-        <v>5.4994855307049875</v>
-      </c>
-      <c r="AE26" s="6">
-        <f t="shared" si="12"/>
         <v>1.7390004558537839</v>
       </c>
       <c r="AF26" s="6">
@@ -27666,15 +27843,15 @@
         <v>8.1502074992717688</v>
       </c>
       <c r="W27" s="6">
+        <f t="shared" si="12"/>
+        <v>1.3229499794410238</v>
+      </c>
+      <c r="X27" s="6">
         <f t="shared" si="13"/>
-        <v>1.3229499794410238</v>
-      </c>
-      <c r="X27" s="6">
+        <v>479.23134033891068</v>
+      </c>
+      <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>479.23134033891068</v>
-      </c>
-      <c r="Y27" s="6">
-        <f t="shared" si="9"/>
         <v>3.240800019855361</v>
       </c>
       <c r="AB27">
@@ -27682,15 +27859,15 @@
         <v>24</v>
       </c>
       <c r="AC27" s="6">
+        <f t="shared" si="9"/>
+        <v>4.4922003213323478</v>
+      </c>
+      <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>4.4922003213323478</v>
-      </c>
-      <c r="AD27" s="6">
+        <v>7.4595712729528714</v>
+      </c>
+      <c r="AE27" s="6">
         <f t="shared" si="11"/>
-        <v>7.4595712729528714</v>
-      </c>
-      <c r="AE27" s="6">
-        <f t="shared" si="12"/>
         <v>2.7814138919222842</v>
       </c>
       <c r="AF27" s="6">
@@ -27778,15 +27955,15 @@
         <v>20.969895287083823</v>
       </c>
       <c r="W28" s="6">
+        <f t="shared" si="12"/>
+        <v>12.925344180455145</v>
+      </c>
+      <c r="X28" s="6">
         <f t="shared" si="13"/>
-        <v>12.925344180455145</v>
-      </c>
-      <c r="X28" s="6">
+        <v>472.65766709430227</v>
+      </c>
+      <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>472.65766709430227</v>
-      </c>
-      <c r="Y28" s="6">
-        <f t="shared" si="9"/>
         <v>3.1787817256062008</v>
       </c>
       <c r="AB28">
@@ -27794,15 +27971,15 @@
         <v>25</v>
       </c>
       <c r="AC28" s="6">
+        <f t="shared" si="9"/>
+        <v>3.4700983991506291</v>
+      </c>
+      <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>3.4700983991506291</v>
-      </c>
-      <c r="AD28" s="6">
+        <v>8.4079884337691055</v>
+      </c>
+      <c r="AE28" s="6">
         <f t="shared" si="11"/>
-        <v>8.4079884337691055</v>
-      </c>
-      <c r="AE28" s="6">
-        <f t="shared" si="12"/>
         <v>4.063099132301204</v>
       </c>
       <c r="AF28" s="6">
@@ -27890,15 +28067,15 @@
         <v>16.53181148219852</v>
       </c>
       <c r="W29" s="6">
+        <f t="shared" si="12"/>
+        <v>1.1520109760392749</v>
+      </c>
+      <c r="X29" s="6">
         <f t="shared" si="13"/>
-        <v>1.1520109760392749</v>
-      </c>
-      <c r="X29" s="6">
+        <v>480.40985014567133</v>
+      </c>
+      <c r="Y29" s="6">
         <f t="shared" si="8"/>
-        <v>480.40985014567133</v>
-      </c>
-      <c r="Y29" s="6">
-        <f t="shared" si="9"/>
         <v>3.1695650710797771</v>
       </c>
       <c r="AB29">
@@ -27906,15 +28083,15 @@
         <v>26</v>
       </c>
       <c r="AC29" s="6">
+        <f t="shared" si="9"/>
+        <v>0.73047308600826</v>
+      </c>
+      <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>0.73047308600826</v>
-      </c>
-      <c r="AD29" s="6">
+        <v>3.3433804442224755</v>
+      </c>
+      <c r="AE29" s="6">
         <f t="shared" si="11"/>
-        <v>3.3433804442224755</v>
-      </c>
-      <c r="AE29" s="6">
-        <f t="shared" si="12"/>
         <v>0.15690983082095045</v>
       </c>
       <c r="AF29" s="6">
@@ -28002,15 +28179,15 @@
         <v>13.08294069803409</v>
       </c>
       <c r="W30" s="6">
+        <f t="shared" si="12"/>
+        <v>5.3322626001270912</v>
+      </c>
+      <c r="X30" s="6">
         <f t="shared" si="13"/>
-        <v>5.3322626001270912</v>
-      </c>
-      <c r="X30" s="6">
+        <v>480.86328043912465</v>
+      </c>
+      <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>480.86328043912465</v>
-      </c>
-      <c r="Y30" s="6">
-        <f t="shared" si="9"/>
         <v>2.9384415855260833</v>
       </c>
       <c r="AB30">
@@ -28018,15 +28195,15 @@
         <v>27</v>
       </c>
       <c r="AC30" s="6">
+        <f t="shared" si="9"/>
+        <v>2.1696688189613269</v>
+      </c>
+      <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>2.1696688189613269</v>
-      </c>
-      <c r="AD30" s="6">
+        <v>5.8867915829737285</v>
+      </c>
+      <c r="AE30" s="6">
         <f t="shared" si="11"/>
-        <v>5.8867915829737285</v>
-      </c>
-      <c r="AE30" s="6">
-        <f t="shared" si="12"/>
         <v>0.97031952617248862</v>
       </c>
       <c r="AF30" s="6">
@@ -28114,15 +28291,15 @@
         <v>16.058547038521425</v>
       </c>
       <c r="W31" s="6">
+        <f t="shared" si="12"/>
+        <v>0.86024194209999294</v>
+      </c>
+      <c r="X31" s="6">
         <f t="shared" si="13"/>
-        <v>0.86024194209999294</v>
-      </c>
-      <c r="X31" s="6">
+        <v>484.2091134713537</v>
+      </c>
+      <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>484.2091134713537</v>
-      </c>
-      <c r="Y31" s="6">
-        <f t="shared" si="9"/>
         <v>2.8822890148588938</v>
       </c>
       <c r="AB31">
@@ -28130,15 +28307,15 @@
         <v>28</v>
       </c>
       <c r="AC31" s="6">
+        <f t="shared" si="9"/>
+        <v>2.774184877831658</v>
+      </c>
+      <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>2.774184877831658</v>
-      </c>
-      <c r="AD31" s="6">
+        <v>4.9627455779966567</v>
+      </c>
+      <c r="AE31" s="6">
         <f t="shared" si="11"/>
-        <v>4.9627455779966567</v>
-      </c>
-      <c r="AE31" s="6">
-        <f t="shared" si="12"/>
         <v>2.0854511578636448</v>
       </c>
       <c r="AF31" s="6">
@@ -28226,15 +28403,15 @@
         <v>14.562445994422108</v>
       </c>
       <c r="W32" s="6">
+        <f t="shared" si="12"/>
+        <v>15.706786028340769</v>
+      </c>
+      <c r="X32" s="6">
         <f t="shared" si="13"/>
-        <v>15.706786028340769</v>
-      </c>
-      <c r="X32" s="6">
+        <v>476.27869904941196</v>
+      </c>
+      <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>476.27869904941196</v>
-      </c>
-      <c r="Y32" s="6">
-        <f t="shared" si="9"/>
         <v>2.9119378764570438</v>
       </c>
       <c r="AB32">
@@ -28242,15 +28419,15 @@
         <v>29</v>
       </c>
       <c r="AC32" s="6">
+        <f t="shared" si="9"/>
+        <v>1.372692861456926</v>
+      </c>
+      <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>1.372692861456926</v>
-      </c>
-      <c r="AD32" s="6">
+        <v>2.0221249966368759</v>
+      </c>
+      <c r="AE32" s="6">
         <f t="shared" si="11"/>
-        <v>2.0221249966368759</v>
-      </c>
-      <c r="AE32" s="6">
-        <f t="shared" si="12"/>
         <v>0.95979432195326808</v>
       </c>
       <c r="AF32" s="6">
@@ -28338,15 +28515,15 @@
         <v>23.310775767624417</v>
       </c>
       <c r="W33" s="6">
+        <f t="shared" si="12"/>
+        <v>-0.18660443245694935</v>
+      </c>
+      <c r="X33" s="6">
         <f t="shared" si="13"/>
-        <v>-0.18660443245694935</v>
-      </c>
-      <c r="X33" s="6">
+        <v>488.11966651046754</v>
+      </c>
+      <c r="Y33" s="6">
         <f t="shared" si="8"/>
-        <v>488.11966651046754</v>
-      </c>
-      <c r="Y33" s="6">
-        <f t="shared" si="9"/>
         <v>3.0280843490413685</v>
       </c>
       <c r="AB33">
@@ -28354,15 +28531,15 @@
         <v>30</v>
       </c>
       <c r="AC33" s="6">
+        <f t="shared" si="9"/>
+        <v>2.579843100791777</v>
+      </c>
+      <c r="AD33" s="6">
         <f t="shared" si="10"/>
-        <v>2.579843100791777</v>
-      </c>
-      <c r="AD33" s="6">
+        <v>2.6348221011849091</v>
+      </c>
+      <c r="AE33" s="6">
         <f t="shared" si="11"/>
-        <v>2.6348221011849091</v>
-      </c>
-      <c r="AE33" s="6">
-        <f t="shared" si="12"/>
         <v>0.52526065858751281</v>
       </c>
       <c r="AF33" s="6">
@@ -28450,15 +28627,15 @@
         <v>12.973140642723424</v>
       </c>
       <c r="W34" s="6">
+        <f t="shared" si="12"/>
+        <v>3.9806867595294726</v>
+      </c>
+      <c r="X34" s="6">
         <f t="shared" si="13"/>
-        <v>3.9806867595294726</v>
-      </c>
-      <c r="X34" s="6">
+        <v>490.00151496114404</v>
+      </c>
+      <c r="Y34" s="6">
         <f t="shared" si="8"/>
-        <v>490.00151496114404</v>
-      </c>
-      <c r="Y34" s="6">
-        <f t="shared" si="9"/>
         <v>3.3698209216708976</v>
       </c>
       <c r="AB34">
@@ -28466,15 +28643,15 @@
         <v>31</v>
       </c>
       <c r="AC34" s="6">
+        <f t="shared" si="9"/>
+        <v>-0.13873849198512289</v>
+      </c>
+      <c r="AD34" s="6">
         <f t="shared" si="10"/>
-        <v>-0.13873849198512289</v>
-      </c>
-      <c r="AD34" s="6">
+        <v>-3.236677149883235</v>
+      </c>
+      <c r="AE34" s="6">
         <f t="shared" si="11"/>
-        <v>-3.236677149883235</v>
-      </c>
-      <c r="AE34" s="6">
-        <f t="shared" si="12"/>
         <v>-0.3517940750946309</v>
       </c>
       <c r="AF34" s="6">
@@ -28562,15 +28739,15 @@
         <v>11.221394485435694</v>
       </c>
       <c r="W35" s="6">
+        <f t="shared" si="12"/>
+        <v>1.2118312687944943</v>
+      </c>
+      <c r="X35" s="6">
         <f t="shared" si="13"/>
-        <v>1.2118312687944943</v>
-      </c>
-      <c r="X35" s="6">
+        <v>493.43230726643918</v>
+      </c>
+      <c r="Y35" s="6">
         <f t="shared" si="8"/>
-        <v>493.43230726643918</v>
-      </c>
-      <c r="Y35" s="6">
-        <f t="shared" si="9"/>
         <v>3.1612751681272666</v>
       </c>
       <c r="AB35">
@@ -28578,15 +28755,15 @@
         <v>32</v>
       </c>
       <c r="AC35" s="6">
+        <f t="shared" si="9"/>
+        <v>-2.511143478953727</v>
+      </c>
+      <c r="AD35" s="6">
         <f t="shared" si="10"/>
-        <v>-2.511143478953727</v>
-      </c>
-      <c r="AD35" s="6">
+        <v>-5.6609194749930793</v>
+      </c>
+      <c r="AE35" s="6">
         <f t="shared" si="11"/>
-        <v>-5.6609194749930793</v>
-      </c>
-      <c r="AE35" s="6">
-        <f t="shared" si="12"/>
         <v>-1.2168290557251566</v>
       </c>
       <c r="AF35" s="6">
@@ -28674,15 +28851,15 @@
         <v>15.028989773105184</v>
       </c>
       <c r="W36" s="6">
+        <f t="shared" si="12"/>
+        <v>15.804351138604833</v>
+      </c>
+      <c r="X36" s="6">
         <f t="shared" si="13"/>
-        <v>15.804351138604833</v>
-      </c>
-      <c r="X36" s="6">
+        <v>484.60047592666501</v>
+      </c>
+      <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>484.60047592666501</v>
-      </c>
-      <c r="Y36" s="6">
-        <f t="shared" si="9"/>
         <v>3.0234842484256657</v>
       </c>
       <c r="AB36">
@@ -28786,15 +28963,15 @@
         <v>16.100518338974858</v>
       </c>
       <c r="W37" s="6">
+        <f t="shared" si="12"/>
+        <v>-1.1156322945844899</v>
+      </c>
+      <c r="X37" s="6">
         <f t="shared" si="13"/>
-        <v>-1.1156322945844899</v>
-      </c>
-      <c r="X37" s="6">
+        <v>492.67058458119885</v>
+      </c>
+      <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>492.67058458119885</v>
-      </c>
-      <c r="Y37" s="6">
-        <f t="shared" si="9"/>
         <v>3.2476673177516484</v>
       </c>
       <c r="AB37">
@@ -28898,15 +29075,15 @@
         <v>14.595638846660087</v>
       </c>
       <c r="W38" s="6">
+        <f t="shared" si="12"/>
+        <v>3.6318275291917779</v>
+      </c>
+      <c r="X38" s="6">
         <f t="shared" si="13"/>
-        <v>3.6318275291917779</v>
-      </c>
-      <c r="X38" s="6">
+        <v>493.67172212220748</v>
+      </c>
+      <c r="Y38" s="6">
         <f t="shared" si="8"/>
-        <v>493.67172212220748</v>
-      </c>
-      <c r="Y38" s="6">
-        <f t="shared" si="9"/>
         <v>3.3792297188547988</v>
       </c>
       <c r="AB38">
@@ -29010,15 +29187,15 @@
         <v>12.662540838562746</v>
       </c>
       <c r="W39" s="6">
+        <f t="shared" si="12"/>
+        <v>1.438054128488897</v>
+      </c>
+      <c r="X39" s="6">
         <f t="shared" si="13"/>
-        <v>1.438054128488897</v>
-      </c>
-      <c r="X39" s="6">
+        <v>495.39037959140148</v>
+      </c>
+      <c r="Y39" s="6">
         <f t="shared" si="8"/>
-        <v>495.39037959140148</v>
-      </c>
-      <c r="Y39" s="6">
-        <f t="shared" si="9"/>
         <v>3.4203434374790254</v>
       </c>
       <c r="AB39">
@@ -29122,15 +29299,15 @@
         <v>17.558389460545381</v>
       </c>
       <c r="W40" s="6">
+        <f t="shared" si="12"/>
+        <v>15.267532605015166</v>
+      </c>
+      <c r="X40" s="6">
         <f t="shared" si="13"/>
-        <v>15.267532605015166</v>
-      </c>
-      <c r="X40" s="6">
+        <v>487.001323021872</v>
+      </c>
+      <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>487.001323021872</v>
-      </c>
-      <c r="Y40" s="6">
-        <f t="shared" si="9"/>
         <v>3.7760518356624591</v>
       </c>
       <c r="AB40">
@@ -29234,15 +29411,15 @@
         <v>15.206623852153969</v>
       </c>
       <c r="W41" s="6">
+        <f t="shared" si="12"/>
+        <v>0.76950621570173183</v>
+      </c>
+      <c r="X41" s="6">
         <f t="shared" si="13"/>
-        <v>0.76950621570173183</v>
-      </c>
-      <c r="X41" s="6">
+        <v>493.87500650544291</v>
+      </c>
+      <c r="Y41" s="6">
         <f t="shared" si="8"/>
-        <v>493.87500650544291</v>
-      </c>
-      <c r="Y41" s="6">
-        <f t="shared" si="9"/>
         <v>3.9619110347789541</v>
       </c>
       <c r="AB41">
@@ -29346,15 +29523,15 @@
         <v>18.277802403087918</v>
       </c>
       <c r="W42" s="6">
+        <f t="shared" si="12"/>
+        <v>7.7263926919048487</v>
+      </c>
+      <c r="X42" s="6">
         <f t="shared" si="13"/>
-        <v>7.7263926919048487</v>
-      </c>
-      <c r="X42" s="6">
+        <v>490.95989160711844</v>
+      </c>
+      <c r="Y42" s="6">
         <f t="shared" si="8"/>
-        <v>490.95989160711844</v>
-      </c>
-      <c r="Y42" s="6">
-        <f t="shared" si="9"/>
         <v>3.9585465888002194</v>
       </c>
       <c r="AB42">
@@ -29458,15 +29635,15 @@
         <v>17.257238504785967</v>
       </c>
       <c r="W43" s="6">
+        <f t="shared" si="12"/>
+        <v>7.7833257735946404</v>
+      </c>
+      <c r="X43" s="6">
         <f t="shared" si="13"/>
-        <v>7.7833257735946404</v>
-      </c>
-      <c r="X43" s="6">
+        <v>487.3139699829328</v>
+      </c>
+      <c r="Y43" s="6">
         <f t="shared" si="8"/>
-        <v>487.3139699829328</v>
-      </c>
-      <c r="Y43" s="6">
-        <f t="shared" si="9"/>
         <v>6.3369895655383255</v>
       </c>
       <c r="AB43">
@@ -29570,15 +29747,15 @@
         <v>9.2097612190712308</v>
       </c>
       <c r="W44" s="6">
+        <f t="shared" si="12"/>
+        <v>19.028616269375043</v>
+      </c>
+      <c r="X44" s="6">
         <f t="shared" si="13"/>
-        <v>19.028616269375043</v>
-      </c>
-      <c r="X44" s="6">
+        <v>478.48452251416364</v>
+      </c>
+      <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>478.48452251416364</v>
-      </c>
-      <c r="Y44" s="6">
-        <f t="shared" si="9"/>
         <v>6.5606816096824545</v>
       </c>
       <c r="AB44">
@@ -29682,15 +29859,15 @@
         <v>11.863508186081059</v>
       </c>
       <c r="W45" s="6">
+        <f t="shared" si="12"/>
+        <v>0.43927994260846148</v>
+      </c>
+      <c r="X45" s="6">
         <f t="shared" si="13"/>
-        <v>0.43927994260846148</v>
-      </c>
-      <c r="X45" s="6">
+        <v>486.4870809246093</v>
+      </c>
+      <c r="Y45" s="6">
         <f t="shared" si="8"/>
-        <v>486.4870809246093</v>
-      </c>
-      <c r="Y45" s="6">
-        <f t="shared" si="9"/>
         <v>6.5193244626190712</v>
       </c>
       <c r="AB45">
@@ -29794,15 +29971,15 @@
         <v>13.756682492830615</v>
       </c>
       <c r="W46" s="6">
+        <f t="shared" si="12"/>
+        <v>6.2170208724188214</v>
+      </c>
+      <c r="X46" s="6">
         <f t="shared" si="13"/>
-        <v>6.2170208724188214</v>
-      </c>
-      <c r="X46" s="6">
+        <v>485.42091032325538</v>
+      </c>
+      <c r="Y46" s="6">
         <f t="shared" si="8"/>
-        <v>485.42091032325538</v>
-      </c>
-      <c r="Y46" s="6">
-        <f t="shared" si="9"/>
         <v>6.6602762566327218</v>
       </c>
       <c r="AB46">
@@ -29906,15 +30083,15 @@
         <v>7.3747228953297315</v>
       </c>
       <c r="W47" s="6">
+        <f t="shared" si="12"/>
+        <v>0.20320580767601015</v>
+      </c>
+      <c r="X47" s="6">
         <f t="shared" si="13"/>
-        <v>0.20320580767601015</v>
-      </c>
-      <c r="X47" s="6">
+        <v>488.32417177095709</v>
+      </c>
+      <c r="Y47" s="6">
         <f t="shared" si="8"/>
-        <v>488.32417177095709</v>
-      </c>
-      <c r="Y47" s="6">
-        <f t="shared" si="9"/>
         <v>6.5823003782786866</v>
       </c>
       <c r="AB47">
@@ -30018,15 +30195,15 @@
         <v>7.1121213056537975</v>
       </c>
       <c r="W48" s="6">
+        <f t="shared" si="12"/>
+        <v>13.057500187965765</v>
+      </c>
+      <c r="X48" s="6">
         <f t="shared" si="13"/>
-        <v>13.057500187965765</v>
-      </c>
-      <c r="X48" s="6">
+        <v>481.94609599614154</v>
+      </c>
+      <c r="Y48" s="6">
         <f t="shared" si="8"/>
-        <v>481.94609599614154</v>
-      </c>
-      <c r="Y48" s="6">
-        <f t="shared" si="9"/>
         <v>6.4582676942278354</v>
       </c>
       <c r="AB48">
@@ -30131,15 +30308,15 @@
         <v>9.7232178953327075</v>
       </c>
       <c r="W49" s="6">
+        <f t="shared" si="12"/>
+        <v>4.6439859884847223</v>
+      </c>
+      <c r="X49" s="6">
         <f t="shared" si="13"/>
-        <v>4.6439859884847223</v>
-      </c>
-      <c r="X49" s="6">
+        <v>486.95913809584346</v>
+      </c>
+      <c r="Y49" s="6">
         <f t="shared" si="8"/>
-        <v>486.95913809584346</v>
-      </c>
-      <c r="Y49" s="6">
-        <f t="shared" si="9"/>
         <v>6.4278000919068949</v>
       </c>
       <c r="AB49">
@@ -30244,15 +30421,15 @@
         <v>15.339387903186315</v>
       </c>
       <c r="W50" s="6">
+        <f t="shared" si="12"/>
+        <v>6.3695213461792299</v>
+      </c>
+      <c r="X50" s="6">
         <f t="shared" si="13"/>
-        <v>6.3695213461792299</v>
-      </c>
-      <c r="X50" s="6">
+        <v>486.17102773842061</v>
+      </c>
+      <c r="Y50" s="6">
         <f t="shared" si="8"/>
-        <v>486.17102773842061</v>
-      </c>
-      <c r="Y50" s="6">
-        <f t="shared" si="9"/>
         <v>7.1943167994809558</v>
       </c>
       <c r="AB50">
@@ -30357,15 +30534,15 @@
         <v>10.718488789774259</v>
       </c>
       <c r="W51" s="6">
+        <f t="shared" si="12"/>
+        <v>7.4470373857877803</v>
+      </c>
+      <c r="X51" s="6">
         <f t="shared" si="13"/>
-        <v>7.4470373857877803</v>
-      </c>
-      <c r="X51" s="6">
+        <v>484.07372964940754</v>
+      </c>
+      <c r="Y51" s="6">
         <f t="shared" si="8"/>
-        <v>484.07372964940754</v>
-      </c>
-      <c r="Y51" s="6">
-        <f t="shared" si="9"/>
         <v>7.3928453487350536</v>
       </c>
       <c r="AB51">
@@ -30469,15 +30646,15 @@
         <v>15.737425172968031</v>
       </c>
       <c r="W52" s="6">
+        <f t="shared" si="12"/>
+        <v>20.019562010454273</v>
+      </c>
+      <c r="X52" s="6">
         <f t="shared" si="13"/>
-        <v>20.019562010454273</v>
-      </c>
-      <c r="X52" s="6">
+        <v>473.98741335761042</v>
+      </c>
+      <c r="Y52" s="6">
         <f t="shared" si="8"/>
-        <v>473.98741335761042</v>
-      </c>
-      <c r="Y52" s="6">
-        <f t="shared" si="9"/>
         <v>7.608995550756581</v>
       </c>
       <c r="AB52">
@@ -30581,15 +30758,15 @@
         <v>13.868529934839632</v>
       </c>
       <c r="W53" s="6">
+        <f t="shared" si="12"/>
+        <v>1.078419910024575</v>
+      </c>
+      <c r="X53" s="6">
         <f t="shared" si="13"/>
-        <v>1.078419910024575</v>
-      </c>
-      <c r="X53" s="6">
+        <v>480.26717846623751</v>
+      </c>
+      <c r="Y53" s="6">
         <f t="shared" si="8"/>
-        <v>480.26717846623751</v>
-      </c>
-      <c r="Y53" s="6">
-        <f t="shared" si="9"/>
         <v>6.5274459744498037</v>
       </c>
       <c r="AB53">
@@ -30693,15 +30870,15 @@
         <v>14.000165616459245</v>
       </c>
       <c r="W54" s="6">
+        <f t="shared" si="12"/>
+        <v>4.3437518168320643</v>
+      </c>
+      <c r="X54" s="6">
         <f t="shared" si="13"/>
-        <v>4.3437518168320643</v>
-      </c>
-      <c r="X54" s="6">
+        <v>482.59346948939969</v>
+      </c>
+      <c r="Y54" s="6">
         <f t="shared" si="8"/>
-        <v>482.59346948939969</v>
-      </c>
-      <c r="Y54" s="6">
-        <f t="shared" si="9"/>
         <v>5.9037963852858901</v>
       </c>
       <c r="AB54">
@@ -30805,15 +30982,15 @@
         <v>15.90249191104482</v>
       </c>
       <c r="W55" s="6">
+        <f t="shared" si="12"/>
+        <v>2.0637106345620992</v>
+      </c>
+      <c r="X55" s="6">
         <f t="shared" si="13"/>
-        <v>2.0637106345620992</v>
-      </c>
-      <c r="X55" s="6">
+        <v>486.45524754908627</v>
+      </c>
+      <c r="Y55" s="6">
         <f t="shared" si="8"/>
-        <v>486.45524754908627</v>
-      </c>
-      <c r="Y55" s="6">
-        <f t="shared" si="9"/>
         <v>5.3605304829877669</v>
       </c>
       <c r="AB55">
@@ -30917,15 +31094,15 @@
         <v>10.810515475482775</v>
       </c>
       <c r="W56" s="6">
+        <f t="shared" si="12"/>
+        <v>12.352179302687283</v>
+      </c>
+      <c r="X56" s="6">
         <f t="shared" si="13"/>
-        <v>12.352179302687283</v>
-      </c>
-      <c r="X56" s="6">
+        <v>480.70103682190785</v>
+      </c>
+      <c r="Y56" s="6">
         <f t="shared" si="8"/>
-        <v>480.70103682190785</v>
-      </c>
-      <c r="Y56" s="6">
-        <f t="shared" si="9"/>
         <v>5.854549803838057</v>
       </c>
       <c r="AB56">
@@ -31029,15 +31206,15 @@
         <v>13.109310057361901</v>
       </c>
       <c r="W57" s="6">
+        <f t="shared" si="12"/>
+        <v>3.8704496392766075</v>
+      </c>
+      <c r="X57" s="6">
         <f t="shared" si="13"/>
-        <v>3.8704496392766075</v>
-      </c>
-      <c r="X57" s="6">
+        <v>484.62927503237376</v>
+      </c>
+      <c r="Y57" s="6">
         <f t="shared" si="8"/>
-        <v>484.62927503237376</v>
-      </c>
-      <c r="Y57" s="6">
-        <f t="shared" si="9"/>
         <v>6.3842429083777024</v>
       </c>
       <c r="AB57">
@@ -31141,15 +31318,15 @@
         <v>14.833792646634885</v>
       </c>
       <c r="W58" s="6">
+        <f t="shared" si="12"/>
+        <v>4.3824238895869172</v>
+      </c>
+      <c r="X58" s="6">
         <f t="shared" si="13"/>
-        <v>4.3824238895869172</v>
-      </c>
-      <c r="X58" s="6">
+        <v>484.42510729813699</v>
+      </c>
+      <c r="Y58" s="6">
         <f t="shared" si="8"/>
-        <v>484.42510729813699</v>
-      </c>
-      <c r="Y58" s="6">
-        <f t="shared" si="9"/>
         <v>6.8204440366212022</v>
       </c>
       <c r="AB58">
@@ -31253,15 +31430,15 @@
         <v>18.482746131479537</v>
       </c>
       <c r="W59" s="6">
+        <f t="shared" si="12"/>
+        <v>6.5899572156119746</v>
+      </c>
+      <c r="X59" s="6">
         <f t="shared" si="13"/>
-        <v>6.5899572156119746</v>
-      </c>
-      <c r="X59" s="6">
+        <v>481.49475626271067</v>
+      </c>
+      <c r="Y59" s="6">
         <f t="shared" si="8"/>
-        <v>481.49475626271067</v>
-      </c>
-      <c r="Y59" s="6">
-        <f t="shared" si="9"/>
         <v>6.2356019099182314</v>
       </c>
       <c r="AB59">
@@ -31365,15 +31542,15 @@
         <v>12.494951445331189</v>
       </c>
       <c r="W60" s="6">
+        <f t="shared" si="12"/>
+        <v>18.965266963906924</v>
+      </c>
+      <c r="X60" s="6">
         <f t="shared" si="13"/>
-        <v>18.965266963906924</v>
-      </c>
-      <c r="X60" s="6">
+        <v>469.27097929558619</v>
+      </c>
+      <c r="Y60" s="6">
         <f t="shared" si="8"/>
-        <v>469.27097929558619</v>
-      </c>
-      <c r="Y60" s="6">
-        <f t="shared" si="9"/>
         <v>9.6975943703528564</v>
       </c>
       <c r="AB60">
@@ -31477,15 +31654,15 @@
         <v>15.060231216500139</v>
       </c>
       <c r="W61" s="6">
+        <f t="shared" si="12"/>
+        <v>5.9907394786250734</v>
+      </c>
+      <c r="X61" s="6">
         <f t="shared" si="13"/>
-        <v>5.9907394786250734</v>
-      </c>
-      <c r="X61" s="6">
+        <v>469.99708646116051</v>
+      </c>
+      <c r="Y61" s="6">
         <f t="shared" si="8"/>
-        <v>469.99708646116051</v>
-      </c>
-      <c r="Y61" s="6">
-        <f t="shared" si="9"/>
         <v>11.741403874034388</v>
       </c>
       <c r="AB61">
@@ -31589,15 +31766,15 @@
         <v>13.533912922575023</v>
       </c>
       <c r="W62" s="6">
+        <f t="shared" si="12"/>
+        <v>11.158607850959434</v>
+      </c>
+      <c r="X62" s="6">
         <f t="shared" si="13"/>
-        <v>11.158607850959434</v>
-      </c>
-      <c r="X62" s="6">
+        <v>467.30392879200161</v>
+      </c>
+      <c r="Y62" s="6">
         <f t="shared" si="8"/>
-        <v>467.30392879200161</v>
-      </c>
-      <c r="Y62" s="6">
-        <f t="shared" si="9"/>
         <v>16.583073965976116</v>
       </c>
       <c r="AB62">
@@ -31701,15 +31878,15 @@
         <v>15.837756655047899</v>
       </c>
       <c r="W63" s="6">
+        <f t="shared" si="12"/>
+        <v>3.5312579409293221</v>
+      </c>
+      <c r="X63" s="6">
         <f t="shared" si="13"/>
-        <v>3.5312579409293221</v>
-      </c>
-      <c r="X63" s="6">
+        <v>472.19147229293145</v>
+      </c>
+      <c r="Y63" s="6">
         <f t="shared" si="8"/>
-        <v>472.19147229293145</v>
-      </c>
-      <c r="Y63" s="6">
-        <f t="shared" si="9"/>
         <v>14.203769446822911</v>
       </c>
       <c r="AB63">
@@ -31813,15 +31990,15 @@
         <v>11.700551273095034</v>
       </c>
       <c r="W64" s="6">
+        <f t="shared" si="12"/>
+        <v>18.886919742323283</v>
+      </c>
+      <c r="X64" s="6">
         <f t="shared" si="13"/>
-        <v>18.886919742323283</v>
-      </c>
-      <c r="X64" s="6">
+        <v>462.91814630149008</v>
+      </c>
+      <c r="Y64" s="6">
         <f t="shared" si="8"/>
-        <v>462.91814630149008</v>
-      </c>
-      <c r="Y64" s="6">
-        <f t="shared" si="9"/>
         <v>17.626286491850074</v>
       </c>
       <c r="AB64">
@@ -31925,15 +32102,15 @@
         <v>11.969923027521993</v>
       </c>
       <c r="W65" s="6">
+        <f t="shared" si="12"/>
+        <v>4.9963527967443966</v>
+      </c>
+      <c r="X65" s="6">
         <f t="shared" si="13"/>
-        <v>4.9963527967443966</v>
-      </c>
-      <c r="X65" s="6">
+        <v>467.9224677587718</v>
+      </c>
+      <c r="Y65" s="6">
         <f t="shared" si="8"/>
-        <v>467.9224677587718</v>
-      </c>
-      <c r="Y65" s="6">
-        <f t="shared" si="9"/>
         <v>18.282307248476869</v>
       </c>
       <c r="AB65">
@@ -32037,15 +32214,15 @@
         <v>13.384613636446357</v>
       </c>
       <c r="W66" s="6">
+        <f t="shared" si="12"/>
+        <v>13.657932758036395</v>
+      </c>
+      <c r="X66" s="6">
         <f t="shared" si="13"/>
-        <v>13.657932758036395</v>
-      </c>
-      <c r="X66" s="6">
+        <v>462.9318552758881</v>
+      </c>
+      <c r="Y66" s="6">
         <f t="shared" si="8"/>
-        <v>462.9318552758881</v>
-      </c>
-      <c r="Y66" s="6">
-        <f t="shared" si="9"/>
         <v>16.584761745055587</v>
       </c>
       <c r="AB66">
@@ -32149,15 +32326,15 @@
         <v>10.528097317889626</v>
       </c>
       <c r="W67" s="6">
+        <f t="shared" si="12"/>
+        <v>3.6497945262150111</v>
+      </c>
+      <c r="X67" s="6">
         <f t="shared" si="13"/>
-        <v>3.6497945262150111</v>
-      </c>
-      <c r="X67" s="6">
+        <v>473.18813317013849</v>
+      </c>
+      <c r="Y67" s="6">
         <f t="shared" si="8"/>
-        <v>473.18813317013849</v>
-      </c>
-      <c r="Y67" s="6">
-        <f t="shared" si="9"/>
         <v>11.376674675963054</v>
       </c>
       <c r="AB67">
@@ -32261,7 +32438,7 @@
         <v>-25.027785571193199</v>
       </c>
       <c r="W68" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>11.276983920016903</v>
       </c>
       <c r="X68" s="6">
@@ -34669,7 +34846,7 @@
     </row>
     <row r="99" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N99" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="14:16" x14ac:dyDescent="0.2">
@@ -34949,20 +35126,20 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="AC4:AI89">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{35AFB368-9982-4EEC-95FE-A7501F31F821}"/>
+    <hyperlink ref="F1" r:id="rId2" xr:uid="{F6291F38-4682-4BD1-80FF-E0F6287A7804}"/>
+    <hyperlink ref="H1" r:id="rId3" xr:uid="{52A39060-918B-4B02-9DB1-58844CF83CEA}"/>
+    <hyperlink ref="J1" r:id="rId4" xr:uid="{63F37E80-123E-4D1D-925B-1CF8A4202AB4}"/>
+    <hyperlink ref="K1" r:id="rId5" xr:uid="{8E232CC2-051B-41A5-AAF0-E20384ED22A4}"/>
+    <hyperlink ref="M1" r:id="rId6" xr:uid="{49E5313B-5736-4449-9990-9151A0D19F5D}"/>
+    <hyperlink ref="O1" r:id="rId7" xr:uid="{11E75FDC-4D2B-4489-8249-CACF09D754A1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>